--- a/data/0000001/샘플.xlsx
+++ b/data/0000001/샘플.xlsx
@@ -397,44 +397,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C3"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>이름</v>
-      </c>
-      <c r="B1" t="str">
-        <v>점수</v>
-      </c>
-      <c r="C1" t="str">
-        <v>등급</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>홍길동</v>
-      </c>
-      <c r="B2">
-        <v>95</v>
-      </c>
-      <c r="C2" t="str">
-        <v>A</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>김철수</v>
-      </c>
-      <c r="B3">
-        <v>88</v>
-      </c>
-      <c r="C3" t="str">
-        <v>B</v>
-      </c>
-    </row>
-  </sheetData>
+  <dimension ref="A1"/>
+  <sheetData/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/0000001/샘플.xlsx
+++ b/data/0000001/샘플.xlsx
@@ -31,28 +31,49 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <color rgb="FFF00F00"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill patternType="none">
+        <bgColor/>
+      </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="gray125">
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -61,13 +82,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="5">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="1" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -397,10 +422,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetData/>
+  <dimension ref="A1:C3"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="2" t="str">
+        <v>sss</v>
+      </c>
+      <c r="C2" s="3" t="str">
+        <v>sss</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="4" t="str">
+        <v>ddd</v>
+      </c>
+    </row>
+  </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C3"/>
   </ignoredErrors>
 </worksheet>
 </file>